--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119994353</v>
       </c>
       <c r="B2" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556441</v>
+        <v>124556583</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491201</v>
+        <v>491182</v>
       </c>
       <c r="R3" t="n">
-        <v>6869719</v>
+        <v>6869761</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556551</v>
+        <v>124556578</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,50 +928,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491196</v>
+        <v>491244</v>
       </c>
       <c r="R4" t="n">
-        <v>6869757</v>
+        <v>6869918</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,12 +1006,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1240,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556621</v>
+        <v>124556759</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,41 +1243,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491247</v>
+        <v>491181</v>
       </c>
       <c r="R7" t="n">
-        <v>6869890</v>
+        <v>6869774</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556543</v>
+        <v>124556618</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,41 +1354,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491251</v>
+        <v>491195</v>
       </c>
       <c r="R8" t="n">
-        <v>6869929</v>
+        <v>6869743</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556773</v>
+        <v>124556543</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491205</v>
+        <v>491251</v>
       </c>
       <c r="R9" t="n">
-        <v>6869833</v>
+        <v>6869929</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556759</v>
+        <v>124556621</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,50 +1567,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491181</v>
+        <v>491247</v>
       </c>
       <c r="R10" t="n">
-        <v>6869774</v>
+        <v>6869890</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556578</v>
+        <v>124556793</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491244</v>
+        <v>491200</v>
       </c>
       <c r="R11" t="n">
-        <v>6869918</v>
+        <v>6869830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556618</v>
+        <v>124556254</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,50 +1873,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491195</v>
+        <v>491211</v>
       </c>
       <c r="R13" t="n">
-        <v>6869743</v>
+        <v>6869621</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,12 +1951,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2074,7 +2065,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556583</v>
+        <v>124556773</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2107,29 +2098,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491182</v>
+        <v>491205</v>
       </c>
       <c r="R15" t="n">
-        <v>6869761</v>
+        <v>6869833</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,22 +2155,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556793</v>
+        <v>124556551</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,41 +2179,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491200</v>
+        <v>491196</v>
       </c>
       <c r="R16" t="n">
-        <v>6869830</v>
+        <v>6869757</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,22 +2266,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556254</v>
+        <v>124556441</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,41 +2290,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491211</v>
+        <v>491201</v>
       </c>
       <c r="R17" t="n">
-        <v>6869621</v>
+        <v>6869719</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556285</v>
+        <v>124556621</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,37 +1034,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491175</v>
+        <v>491247</v>
       </c>
       <c r="R5" t="n">
-        <v>6869662</v>
+        <v>6869890</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556653</v>
+        <v>124556285</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,47 +1132,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491188</v>
+        <v>491175</v>
       </c>
       <c r="R6" t="n">
-        <v>6869772</v>
+        <v>6869662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556759</v>
+        <v>124556551</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1280,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491181</v>
+        <v>491196</v>
       </c>
       <c r="R7" t="n">
-        <v>6869774</v>
+        <v>6869757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556618</v>
+        <v>124556793</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,50 +1345,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491195</v>
+        <v>491200</v>
       </c>
       <c r="R8" t="n">
-        <v>6869743</v>
+        <v>6869830</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1423,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556543</v>
+        <v>124556254</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491251</v>
+        <v>491211</v>
       </c>
       <c r="R9" t="n">
-        <v>6869929</v>
+        <v>6869621</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1555,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556621</v>
+        <v>124556653</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,41 +1549,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491247</v>
+        <v>491188</v>
       </c>
       <c r="R10" t="n">
-        <v>6869890</v>
+        <v>6869772</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556793</v>
+        <v>124556618</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,41 +1660,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491200</v>
+        <v>491195</v>
       </c>
       <c r="R11" t="n">
-        <v>6869830</v>
+        <v>6869743</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,22 +1747,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556457</v>
+        <v>124556759</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,41 +1771,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491199</v>
+        <v>491181</v>
       </c>
       <c r="R12" t="n">
-        <v>6869700</v>
+        <v>6869774</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556254</v>
+        <v>124556457</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,37 +1886,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491211</v>
+        <v>491199</v>
       </c>
       <c r="R13" t="n">
-        <v>6869621</v>
+        <v>6869700</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556648</v>
+        <v>124556441</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,41 +1984,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491217</v>
+        <v>491201</v>
       </c>
       <c r="R14" t="n">
-        <v>6869897</v>
+        <v>6869719</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,12 +2071,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2167,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556551</v>
+        <v>124556543</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,50 +2197,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491196</v>
+        <v>491251</v>
       </c>
       <c r="R16" t="n">
-        <v>6869757</v>
+        <v>6869929</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,22 +2275,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556441</v>
+        <v>124556648</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,50 +2299,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491201</v>
+        <v>491217</v>
       </c>
       <c r="R17" t="n">
-        <v>6869719</v>
+        <v>6869897</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556583</v>
+        <v>124556648</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,50 +817,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491182</v>
+        <v>491217</v>
       </c>
       <c r="R3" t="n">
-        <v>6869761</v>
+        <v>6869897</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556578</v>
+        <v>124556543</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491244</v>
+        <v>491251</v>
       </c>
       <c r="R4" t="n">
-        <v>6869918</v>
+        <v>6869929</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556621</v>
+        <v>124556285</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,37 +1025,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491247</v>
+        <v>491175</v>
       </c>
       <c r="R5" t="n">
-        <v>6869890</v>
+        <v>6869662</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556285</v>
+        <v>124556441</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,38 +1123,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491175</v>
+        <v>491201</v>
       </c>
       <c r="R6" t="n">
-        <v>6869662</v>
+        <v>6869719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556551</v>
+        <v>124556773</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1255,29 +1255,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491196</v>
+        <v>491205</v>
       </c>
       <c r="R7" t="n">
-        <v>6869757</v>
+        <v>6869833</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,22 +1312,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556793</v>
+        <v>124556583</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,41 +1336,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491200</v>
+        <v>491182</v>
       </c>
       <c r="R8" t="n">
-        <v>6869830</v>
+        <v>6869761</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,22 +1423,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556254</v>
+        <v>124556457</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,37 +1451,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491211</v>
+        <v>491199</v>
       </c>
       <c r="R9" t="n">
-        <v>6869621</v>
+        <v>6869700</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,22 +1525,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556653</v>
+        <v>124556578</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,47 +1549,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491188</v>
+        <v>491244</v>
       </c>
       <c r="R10" t="n">
-        <v>6869772</v>
+        <v>6869918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,19 +1627,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556618</v>
+        <v>124556759</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1683,7 +1674,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1697,13 +1688,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491195</v>
+        <v>491181</v>
       </c>
       <c r="R11" t="n">
-        <v>6869743</v>
+        <v>6869774</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556759</v>
+        <v>124556254</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,50 +1762,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491181</v>
+        <v>491211</v>
       </c>
       <c r="R12" t="n">
-        <v>6869774</v>
+        <v>6869621</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,22 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556457</v>
+        <v>124556551</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,38 +1864,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491199</v>
+        <v>491196</v>
       </c>
       <c r="R13" t="n">
-        <v>6869700</v>
+        <v>6869757</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1972,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556441</v>
+        <v>124556653</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2007,7 +1998,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2017,14 +2008,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491201</v>
+        <v>491188</v>
       </c>
       <c r="R14" t="n">
-        <v>6869719</v>
+        <v>6869772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556773</v>
+        <v>124556621</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,25 +2086,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,13 +2114,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491205</v>
+        <v>491247</v>
       </c>
       <c r="R15" t="n">
-        <v>6869833</v>
+        <v>6869890</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556543</v>
+        <v>124556618</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,41 +2188,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491251</v>
+        <v>491195</v>
       </c>
       <c r="R16" t="n">
-        <v>6869929</v>
+        <v>6869743</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,19 +2275,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556648</v>
+        <v>124556793</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491217</v>
+        <v>491200</v>
       </c>
       <c r="R17" t="n">
-        <v>6869897</v>
+        <v>6869830</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556648</v>
+        <v>124556773</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491217</v>
+        <v>491205</v>
       </c>
       <c r="R3" t="n">
-        <v>6869897</v>
+        <v>6869833</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556543</v>
+        <v>124556621</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491251</v>
+        <v>491247</v>
       </c>
       <c r="R4" t="n">
-        <v>6869929</v>
+        <v>6869890</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556285</v>
+        <v>124556543</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,37 +1025,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491175</v>
+        <v>491251</v>
       </c>
       <c r="R5" t="n">
-        <v>6869662</v>
+        <v>6869929</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1099,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556441</v>
+        <v>124556653</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1156,14 +1156,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491201</v>
+        <v>491188</v>
       </c>
       <c r="R6" t="n">
-        <v>6869719</v>
+        <v>6869772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556773</v>
+        <v>124556759</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1255,17 +1255,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491205</v>
+        <v>491181</v>
       </c>
       <c r="R7" t="n">
-        <v>6869833</v>
+        <v>6869774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,19 +1321,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556583</v>
+        <v>124556551</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1359,7 +1368,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1373,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491182</v>
+        <v>491196</v>
       </c>
       <c r="R8" t="n">
-        <v>6869761</v>
+        <v>6869757</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1435,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556457</v>
+        <v>124556254</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,37 +1460,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491199</v>
+        <v>491211</v>
       </c>
       <c r="R9" t="n">
-        <v>6869700</v>
+        <v>6869621</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1639,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556759</v>
+        <v>124556457</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,50 +1660,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491181</v>
+        <v>491199</v>
       </c>
       <c r="R11" t="n">
-        <v>6869774</v>
+        <v>6869700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556254</v>
+        <v>124556793</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491211</v>
+        <v>491200</v>
       </c>
       <c r="R12" t="n">
-        <v>6869621</v>
+        <v>6869830</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556551</v>
+        <v>124556618</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491196</v>
+        <v>491195</v>
       </c>
       <c r="R13" t="n">
-        <v>6869757</v>
+        <v>6869743</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556653</v>
+        <v>124556285</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,47 +1975,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491188</v>
+        <v>491175</v>
       </c>
       <c r="R14" t="n">
-        <v>6869772</v>
+        <v>6869662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556621</v>
+        <v>124556648</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2081,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491247</v>
+        <v>491217</v>
       </c>
       <c r="R15" t="n">
-        <v>6869890</v>
+        <v>6869897</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2176,7 +2167,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556618</v>
+        <v>124556583</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2211,7 +2202,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2225,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491195</v>
+        <v>491182</v>
       </c>
       <c r="R16" t="n">
-        <v>6869743</v>
+        <v>6869761</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2287,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556793</v>
+        <v>124556441</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,38 +2290,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491200</v>
+        <v>491201</v>
       </c>
       <c r="R17" t="n">
-        <v>6869830</v>
+        <v>6869719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556621</v>
+        <v>124556543</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491247</v>
+        <v>491251</v>
       </c>
       <c r="R4" t="n">
-        <v>6869890</v>
+        <v>6869929</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556543</v>
+        <v>124556621</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491251</v>
+        <v>491247</v>
       </c>
       <c r="R5" t="n">
-        <v>6869929</v>
+        <v>6869890</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556773</v>
+        <v>124556254</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491205</v>
+        <v>491211</v>
       </c>
       <c r="R3" t="n">
-        <v>6869833</v>
+        <v>6869621</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556543</v>
+        <v>124556285</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,37 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491251</v>
+        <v>491175</v>
       </c>
       <c r="R4" t="n">
-        <v>6869929</v>
+        <v>6869662</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556621</v>
+        <v>124556543</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491247</v>
+        <v>491251</v>
       </c>
       <c r="R5" t="n">
-        <v>6869890</v>
+        <v>6869929</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556653</v>
+        <v>124556457</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,50 +1123,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491188</v>
+        <v>491199</v>
       </c>
       <c r="R6" t="n">
-        <v>6869772</v>
+        <v>6869700</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556759</v>
+        <v>124556653</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1257,7 +1248,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1271,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491181</v>
+        <v>491188</v>
       </c>
       <c r="R7" t="n">
-        <v>6869774</v>
+        <v>6869772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556551</v>
+        <v>124556621</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,50 +1336,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491196</v>
+        <v>491247</v>
       </c>
       <c r="R8" t="n">
-        <v>6869757</v>
+        <v>6869890</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1414,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556254</v>
+        <v>124556773</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1438,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1466,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491211</v>
+        <v>491205</v>
       </c>
       <c r="R9" t="n">
-        <v>6869621</v>
+        <v>6869833</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556578</v>
+        <v>124556551</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,41 +1540,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491244</v>
+        <v>491196</v>
       </c>
       <c r="R10" t="n">
-        <v>6869918</v>
+        <v>6869757</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,22 +1627,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556457</v>
+        <v>124556759</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,41 +1651,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491199</v>
+        <v>491181</v>
       </c>
       <c r="R11" t="n">
-        <v>6869700</v>
+        <v>6869774</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556793</v>
+        <v>124556583</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,41 +1762,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491200</v>
+        <v>491182</v>
       </c>
       <c r="R12" t="n">
-        <v>6869830</v>
+        <v>6869761</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,12 +1849,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1963,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556285</v>
+        <v>124556793</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,34 +1988,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491175</v>
+        <v>491200</v>
       </c>
       <c r="R14" t="n">
-        <v>6869662</v>
+        <v>6869830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2167,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556583</v>
+        <v>124556441</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2202,7 +2211,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2212,17 +2221,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491182</v>
+        <v>491201</v>
       </c>
       <c r="R16" t="n">
-        <v>6869761</v>
+        <v>6869719</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2278,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556441</v>
+        <v>124556578</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,47 +2299,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491201</v>
+        <v>491244</v>
       </c>
       <c r="R17" t="n">
-        <v>6869719</v>
+        <v>6869918</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556457</v>
+        <v>124556653</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,41 +1123,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491199</v>
+        <v>491188</v>
       </c>
       <c r="R6" t="n">
-        <v>6869700</v>
+        <v>6869772</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556653</v>
+        <v>124556457</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,50 +1234,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491188</v>
+        <v>491199</v>
       </c>
       <c r="R7" t="n">
-        <v>6869772</v>
+        <v>6869700</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556254</v>
+        <v>124556441</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,41 +817,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491211</v>
+        <v>491201</v>
       </c>
       <c r="R3" t="n">
-        <v>6869621</v>
+        <v>6869719</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556285</v>
+        <v>124556583</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,41 +928,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491175</v>
+        <v>491182</v>
       </c>
       <c r="R4" t="n">
-        <v>6869662</v>
+        <v>6869761</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556543</v>
+        <v>124556254</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491251</v>
+        <v>491211</v>
       </c>
       <c r="R5" t="n">
-        <v>6869929</v>
+        <v>6869621</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1222,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556457</v>
+        <v>124556618</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,38 +1252,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491199</v>
+        <v>491195</v>
       </c>
       <c r="R7" t="n">
-        <v>6869700</v>
+        <v>6869743</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1426,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556773</v>
+        <v>124556648</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491205</v>
+        <v>491217</v>
       </c>
       <c r="R9" t="n">
-        <v>6869833</v>
+        <v>6869897</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556551</v>
+        <v>124556457</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,47 +1567,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491196</v>
+        <v>491199</v>
       </c>
       <c r="R10" t="n">
-        <v>6869757</v>
+        <v>6869700</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1750,7 +1768,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556583</v>
+        <v>124556551</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1785,7 +1803,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1799,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491182</v>
+        <v>491196</v>
       </c>
       <c r="R12" t="n">
-        <v>6869761</v>
+        <v>6869757</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1861,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556618</v>
+        <v>124556773</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1894,29 +1912,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491195</v>
+        <v>491205</v>
       </c>
       <c r="R13" t="n">
-        <v>6869743</v>
+        <v>6869833</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,22 +1969,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556793</v>
+        <v>124556285</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,34 +1997,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491200</v>
+        <v>491175</v>
       </c>
       <c r="R14" t="n">
-        <v>6869830</v>
+        <v>6869662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,19 +2071,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556648</v>
+        <v>124556793</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2114,13 +2123,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491217</v>
+        <v>491200</v>
       </c>
       <c r="R15" t="n">
-        <v>6869897</v>
+        <v>6869830</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556441</v>
+        <v>124556578</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,47 +2197,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491201</v>
+        <v>491244</v>
       </c>
       <c r="R16" t="n">
-        <v>6869719</v>
+        <v>6869918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,22 +2275,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556578</v>
+        <v>124556543</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,21 +2303,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491244</v>
+        <v>491251</v>
       </c>
       <c r="R17" t="n">
-        <v>6869918</v>
+        <v>6869929</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556441</v>
+        <v>124556648</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,50 +817,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491201</v>
+        <v>491217</v>
       </c>
       <c r="R3" t="n">
-        <v>6869719</v>
+        <v>6869897</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556583</v>
+        <v>124556457</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,47 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491182</v>
+        <v>491199</v>
       </c>
       <c r="R4" t="n">
-        <v>6869761</v>
+        <v>6869700</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1027,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556254</v>
+        <v>124556543</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491211</v>
+        <v>491251</v>
       </c>
       <c r="R5" t="n">
-        <v>6869621</v>
+        <v>6869929</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1129,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556653</v>
+        <v>124556759</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1164,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1178,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491188</v>
+        <v>491181</v>
       </c>
       <c r="R6" t="n">
-        <v>6869772</v>
+        <v>6869774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556618</v>
+        <v>124556551</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1275,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491195</v>
+        <v>491196</v>
       </c>
       <c r="R7" t="n">
-        <v>6869743</v>
+        <v>6869757</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1351,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556621</v>
+        <v>124556254</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491247</v>
+        <v>491211</v>
       </c>
       <c r="R8" t="n">
-        <v>6869890</v>
+        <v>6869621</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1453,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556648</v>
+        <v>124556773</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491217</v>
+        <v>491205</v>
       </c>
       <c r="R9" t="n">
-        <v>6869897</v>
+        <v>6869833</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1555,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556457</v>
+        <v>124556285</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491199</v>
+        <v>491175</v>
       </c>
       <c r="R10" t="n">
-        <v>6869700</v>
+        <v>6869662</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556759</v>
+        <v>124556621</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,50 +1651,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491181</v>
+        <v>491247</v>
       </c>
       <c r="R11" t="n">
-        <v>6869774</v>
+        <v>6869890</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,19 +1729,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556551</v>
+        <v>124556653</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1803,7 +1776,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1817,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491196</v>
+        <v>491188</v>
       </c>
       <c r="R12" t="n">
-        <v>6869757</v>
+        <v>6869772</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556773</v>
+        <v>124556618</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1912,20 +1885,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491205</v>
+        <v>491195</v>
       </c>
       <c r="R13" t="n">
-        <v>6869833</v>
+        <v>6869743</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,22 +1951,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556285</v>
+        <v>124556583</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,41 +1975,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491175</v>
+        <v>491182</v>
       </c>
       <c r="R14" t="n">
-        <v>6869662</v>
+        <v>6869761</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2287,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556543</v>
+        <v>124556441</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,41 +2290,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491251</v>
+        <v>491201</v>
       </c>
       <c r="R17" t="n">
-        <v>6869929</v>
+        <v>6869719</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556621</v>
+        <v>124556653</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,41 +1651,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491247</v>
+        <v>491188</v>
       </c>
       <c r="R11" t="n">
-        <v>6869890</v>
+        <v>6869772</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556653</v>
+        <v>124556621</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,50 +1762,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491188</v>
+        <v>491247</v>
       </c>
       <c r="R12" t="n">
-        <v>6869772</v>
+        <v>6869890</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556648</v>
+        <v>124556621</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491217</v>
+        <v>491247</v>
       </c>
       <c r="R3" t="n">
-        <v>6869897</v>
+        <v>6869890</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556457</v>
+        <v>124556648</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -943,17 +943,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491199</v>
+        <v>491217</v>
       </c>
       <c r="R4" t="n">
-        <v>6869700</v>
+        <v>6869897</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,19 +997,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556543</v>
+        <v>124556457</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1045,17 +1045,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491251</v>
+        <v>491199</v>
       </c>
       <c r="R5" t="n">
-        <v>6869929</v>
+        <v>6869700</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556759</v>
+        <v>124556543</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,50 +1123,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491181</v>
+        <v>491251</v>
       </c>
       <c r="R6" t="n">
-        <v>6869774</v>
+        <v>6869929</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1201,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556551</v>
+        <v>124556759</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1257,7 +1248,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1271,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491196</v>
+        <v>491181</v>
       </c>
       <c r="R7" t="n">
-        <v>6869757</v>
+        <v>6869774</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1435,7 +1426,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556773</v>
+        <v>124556441</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1468,17 +1459,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491205</v>
+        <v>491201</v>
       </c>
       <c r="R9" t="n">
-        <v>6869833</v>
+        <v>6869719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,22 +1525,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556285</v>
+        <v>124556583</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,41 +1549,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491175</v>
+        <v>491182</v>
       </c>
       <c r="R10" t="n">
-        <v>6869662</v>
+        <v>6869761</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556653</v>
+        <v>124556618</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1674,7 +1683,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1688,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491188</v>
+        <v>491195</v>
       </c>
       <c r="R11" t="n">
-        <v>6869772</v>
+        <v>6869743</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556621</v>
+        <v>124556285</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,37 +1775,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491247</v>
+        <v>491175</v>
       </c>
       <c r="R12" t="n">
-        <v>6869890</v>
+        <v>6869662</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556618</v>
+        <v>124556793</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,50 +1873,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491195</v>
+        <v>491200</v>
       </c>
       <c r="R13" t="n">
-        <v>6869743</v>
+        <v>6869830</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,19 +1951,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556583</v>
+        <v>124556653</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491182</v>
+        <v>491188</v>
       </c>
       <c r="R14" t="n">
-        <v>6869761</v>
+        <v>6869772</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556793</v>
+        <v>124556578</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491200</v>
+        <v>491244</v>
       </c>
       <c r="R15" t="n">
-        <v>6869830</v>
+        <v>6869918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556578</v>
+        <v>124556773</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,25 +2188,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491244</v>
+        <v>491205</v>
       </c>
       <c r="R16" t="n">
-        <v>6869918</v>
+        <v>6869833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556441</v>
+        <v>124556551</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491201</v>
+        <v>491196</v>
       </c>
       <c r="R17" t="n">
-        <v>6869719</v>
+        <v>6869757</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556621</v>
+        <v>124556285</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,37 +821,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491247</v>
+        <v>491175</v>
       </c>
       <c r="R3" t="n">
-        <v>6869890</v>
+        <v>6869662</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556648</v>
+        <v>124556618</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,41 +919,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491217</v>
+        <v>491195</v>
       </c>
       <c r="R4" t="n">
-        <v>6869897</v>
+        <v>6869743</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556457</v>
+        <v>124556441</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,41 +1030,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491199</v>
+        <v>491201</v>
       </c>
       <c r="R5" t="n">
-        <v>6869700</v>
+        <v>6869719</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556543</v>
+        <v>124556793</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1151,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491251</v>
+        <v>491200</v>
       </c>
       <c r="R6" t="n">
-        <v>6869929</v>
+        <v>6869830</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556759</v>
+        <v>124556653</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1248,7 +1266,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1262,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491181</v>
+        <v>491188</v>
       </c>
       <c r="R7" t="n">
-        <v>6869774</v>
+        <v>6869772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556254</v>
+        <v>124556621</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491211</v>
+        <v>491247</v>
       </c>
       <c r="R8" t="n">
-        <v>6869621</v>
+        <v>6869890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1426,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556441</v>
+        <v>124556773</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1459,26 +1477,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491201</v>
+        <v>491205</v>
       </c>
       <c r="R9" t="n">
-        <v>6869719</v>
+        <v>6869833</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1648,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556618</v>
+        <v>124556457</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,47 +1669,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491195</v>
+        <v>491199</v>
       </c>
       <c r="R11" t="n">
-        <v>6869743</v>
+        <v>6869700</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556285</v>
+        <v>124556648</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,37 +1775,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491175</v>
+        <v>491217</v>
       </c>
       <c r="R12" t="n">
-        <v>6869662</v>
+        <v>6869897</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556793</v>
+        <v>124556578</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491200</v>
+        <v>491244</v>
       </c>
       <c r="R13" t="n">
-        <v>6869830</v>
+        <v>6869918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556653</v>
+        <v>124556254</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,50 +1975,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491188</v>
+        <v>491211</v>
       </c>
       <c r="R14" t="n">
-        <v>6869772</v>
+        <v>6869621</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,22 +2053,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556578</v>
+        <v>124556551</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,41 +2077,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491244</v>
+        <v>491196</v>
       </c>
       <c r="R15" t="n">
-        <v>6869918</v>
+        <v>6869757</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,22 +2164,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556773</v>
+        <v>124556543</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,25 +2188,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491205</v>
+        <v>491251</v>
       </c>
       <c r="R16" t="n">
-        <v>6869833</v>
+        <v>6869929</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556551</v>
+        <v>124556759</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491196</v>
+        <v>491181</v>
       </c>
       <c r="R17" t="n">
-        <v>6869757</v>
+        <v>6869774</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556285</v>
+        <v>124556578</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491175</v>
+        <v>491244</v>
       </c>
       <c r="R3" t="n">
-        <v>6869662</v>
+        <v>6869918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,12 +895,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556441</v>
+        <v>124556621</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,50 +1030,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491201</v>
+        <v>491247</v>
       </c>
       <c r="R5" t="n">
-        <v>6869719</v>
+        <v>6869890</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,19 +1108,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556793</v>
+        <v>124556543</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1169,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491200</v>
+        <v>491251</v>
       </c>
       <c r="R6" t="n">
-        <v>6869830</v>
+        <v>6869929</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556653</v>
+        <v>124556759</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1280,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491188</v>
+        <v>491181</v>
       </c>
       <c r="R7" t="n">
-        <v>6869772</v>
+        <v>6869774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556621</v>
+        <v>124556441</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,41 +1345,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491247</v>
+        <v>491201</v>
       </c>
       <c r="R8" t="n">
-        <v>6869890</v>
+        <v>6869719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556773</v>
+        <v>124556793</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1456,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491205</v>
+        <v>491200</v>
       </c>
       <c r="R9" t="n">
-        <v>6869833</v>
+        <v>6869830</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556583</v>
+        <v>124556285</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,50 +1558,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491182</v>
+        <v>491175</v>
       </c>
       <c r="R10" t="n">
-        <v>6869761</v>
+        <v>6869662</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556457</v>
+        <v>124556254</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,37 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491199</v>
+        <v>491211</v>
       </c>
       <c r="R11" t="n">
-        <v>6869700</v>
+        <v>6869621</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556648</v>
+        <v>124556653</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,41 +1762,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491217</v>
+        <v>491188</v>
       </c>
       <c r="R12" t="n">
-        <v>6869897</v>
+        <v>6869772</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556578</v>
+        <v>124556551</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,41 +1873,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491244</v>
+        <v>491196</v>
       </c>
       <c r="R13" t="n">
-        <v>6869918</v>
+        <v>6869757</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556254</v>
+        <v>124556583</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,41 +1984,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491211</v>
+        <v>491182</v>
       </c>
       <c r="R14" t="n">
-        <v>6869621</v>
+        <v>6869761</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,22 +2071,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556551</v>
+        <v>124556457</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,47 +2095,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491196</v>
+        <v>491199</v>
       </c>
       <c r="R15" t="n">
-        <v>6869757</v>
+        <v>6869700</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2176,7 +2185,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556543</v>
+        <v>124556648</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2216,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491251</v>
+        <v>491217</v>
       </c>
       <c r="R16" t="n">
-        <v>6869929</v>
+        <v>6869897</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2278,7 +2287,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556759</v>
+        <v>124556773</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2311,26 +2320,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491181</v>
+        <v>491205</v>
       </c>
       <c r="R17" t="n">
-        <v>6869774</v>
+        <v>6869833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556578</v>
+        <v>124556551</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,41 +817,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491244</v>
+        <v>491196</v>
       </c>
       <c r="R3" t="n">
-        <v>6869918</v>
+        <v>6869757</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556618</v>
+        <v>124556543</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,50 +928,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491195</v>
+        <v>491251</v>
       </c>
       <c r="R4" t="n">
-        <v>6869743</v>
+        <v>6869929</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556621</v>
+        <v>124556793</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491247</v>
+        <v>491200</v>
       </c>
       <c r="R5" t="n">
-        <v>6869890</v>
+        <v>6869830</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556543</v>
+        <v>124556653</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,41 +1132,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491251</v>
+        <v>491188</v>
       </c>
       <c r="R6" t="n">
-        <v>6869929</v>
+        <v>6869772</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1219,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556759</v>
+        <v>124556583</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1257,7 +1266,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1271,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491181</v>
+        <v>491182</v>
       </c>
       <c r="R7" t="n">
-        <v>6869774</v>
+        <v>6869761</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556441</v>
+        <v>124556457</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,50 +1354,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491201</v>
+        <v>491199</v>
       </c>
       <c r="R8" t="n">
-        <v>6869719</v>
+        <v>6869700</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556793</v>
+        <v>124556648</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491200</v>
+        <v>491217</v>
       </c>
       <c r="R9" t="n">
-        <v>6869830</v>
+        <v>6869897</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556285</v>
+        <v>124556621</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,37 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491175</v>
+        <v>491247</v>
       </c>
       <c r="R10" t="n">
-        <v>6869662</v>
+        <v>6869890</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556254</v>
+        <v>124556618</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,41 +1660,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491211</v>
+        <v>491195</v>
       </c>
       <c r="R11" t="n">
-        <v>6869621</v>
+        <v>6869743</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,19 +1747,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556653</v>
+        <v>124556759</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1785,7 +1794,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1799,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491188</v>
+        <v>491181</v>
       </c>
       <c r="R12" t="n">
-        <v>6869772</v>
+        <v>6869774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556551</v>
+        <v>124556254</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,50 +1882,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491196</v>
+        <v>491211</v>
       </c>
       <c r="R13" t="n">
-        <v>6869757</v>
+        <v>6869621</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556583</v>
+        <v>124556285</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,50 +1984,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491182</v>
+        <v>491175</v>
       </c>
       <c r="R14" t="n">
-        <v>6869761</v>
+        <v>6869662</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556457</v>
+        <v>124556773</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,41 +2086,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491199</v>
+        <v>491205</v>
       </c>
       <c r="R15" t="n">
-        <v>6869700</v>
+        <v>6869833</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,22 +2164,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556648</v>
+        <v>124556441</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,41 +2188,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491217</v>
+        <v>491201</v>
       </c>
       <c r="R16" t="n">
-        <v>6869897</v>
+        <v>6869719</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,22 +2275,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556773</v>
+        <v>124556578</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,25 +2299,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491205</v>
+        <v>491244</v>
       </c>
       <c r="R17" t="n">
-        <v>6869833</v>
+        <v>6869918</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556551</v>
+        <v>124556285</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,50 +817,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491196</v>
+        <v>491175</v>
       </c>
       <c r="R3" t="n">
-        <v>6869757</v>
+        <v>6869662</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556543</v>
+        <v>124556759</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,41 +919,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491251</v>
+        <v>491181</v>
       </c>
       <c r="R4" t="n">
-        <v>6869929</v>
+        <v>6869774</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,12 +1006,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556653</v>
+        <v>124556441</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,14 +1165,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491188</v>
+        <v>491201</v>
       </c>
       <c r="R6" t="n">
-        <v>6869772</v>
+        <v>6869719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556583</v>
+        <v>124556457</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,47 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491182</v>
+        <v>491199</v>
       </c>
       <c r="R7" t="n">
-        <v>6869761</v>
+        <v>6869700</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1342,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556457</v>
+        <v>124556583</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,38 +1345,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491199</v>
+        <v>491182</v>
       </c>
       <c r="R8" t="n">
-        <v>6869700</v>
+        <v>6869761</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556648</v>
+        <v>124556773</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1456,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491217</v>
+        <v>491205</v>
       </c>
       <c r="R9" t="n">
-        <v>6869897</v>
+        <v>6869833</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556618</v>
+        <v>124556653</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491195</v>
+        <v>491188</v>
       </c>
       <c r="R11" t="n">
-        <v>6869743</v>
+        <v>6869772</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556759</v>
+        <v>124556648</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,50 +1771,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491181</v>
+        <v>491217</v>
       </c>
       <c r="R12" t="n">
-        <v>6869774</v>
+        <v>6869897</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556254</v>
+        <v>124556618</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,41 +1873,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491211</v>
+        <v>491195</v>
       </c>
       <c r="R13" t="n">
-        <v>6869621</v>
+        <v>6869743</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556285</v>
+        <v>124556543</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,37 +1988,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491175</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6869662</v>
+        <v>6869929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,19 +2062,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556773</v>
+        <v>124556551</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2107,20 +2107,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491205</v>
+        <v>491196</v>
       </c>
       <c r="R15" t="n">
-        <v>6869833</v>
+        <v>6869757</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,22 +2173,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556441</v>
+        <v>124556254</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,50 +2197,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491201</v>
+        <v>491211</v>
       </c>
       <c r="R16" t="n">
-        <v>6869719</v>
+        <v>6869621</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,12 +2275,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556285</v>
+        <v>124556583</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,41 +817,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491175</v>
+        <v>491182</v>
       </c>
       <c r="R3" t="n">
-        <v>6869662</v>
+        <v>6869761</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556759</v>
+        <v>124556653</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -942,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -956,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491181</v>
+        <v>491188</v>
       </c>
       <c r="R4" t="n">
-        <v>6869774</v>
+        <v>6869772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556793</v>
+        <v>124556441</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,38 +1039,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491200</v>
+        <v>491201</v>
       </c>
       <c r="R5" t="n">
-        <v>6869830</v>
+        <v>6869719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556441</v>
+        <v>124556621</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,50 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491201</v>
+        <v>491247</v>
       </c>
       <c r="R6" t="n">
-        <v>6869719</v>
+        <v>6869890</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556457</v>
+        <v>124556578</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,37 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491199</v>
+        <v>491244</v>
       </c>
       <c r="R7" t="n">
-        <v>6869700</v>
+        <v>6869918</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,19 +1330,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556583</v>
+        <v>124556618</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1368,7 +1377,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1382,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491182</v>
+        <v>491195</v>
       </c>
       <c r="R8" t="n">
-        <v>6869761</v>
+        <v>6869743</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1444,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556773</v>
+        <v>124556648</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491205</v>
+        <v>491217</v>
       </c>
       <c r="R9" t="n">
-        <v>6869833</v>
+        <v>6869897</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556621</v>
+        <v>124556543</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491247</v>
+        <v>491251</v>
       </c>
       <c r="R10" t="n">
-        <v>6869890</v>
+        <v>6869929</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1648,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556653</v>
+        <v>124556793</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,47 +1669,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491188</v>
+        <v>491200</v>
       </c>
       <c r="R11" t="n">
-        <v>6869772</v>
+        <v>6869830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,22 +1747,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556648</v>
+        <v>124556551</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,41 +1771,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491217</v>
+        <v>491196</v>
       </c>
       <c r="R12" t="n">
-        <v>6869897</v>
+        <v>6869757</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,22 +1858,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556618</v>
+        <v>124556285</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,50 +1882,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491195</v>
+        <v>491175</v>
       </c>
       <c r="R13" t="n">
-        <v>6869743</v>
+        <v>6869662</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556543</v>
+        <v>124556773</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491205</v>
       </c>
       <c r="R14" t="n">
-        <v>6869929</v>
+        <v>6869833</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556551</v>
+        <v>124556457</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,47 +2086,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491196</v>
+        <v>491199</v>
       </c>
       <c r="R15" t="n">
-        <v>6869757</v>
+        <v>6869700</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2287,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556578</v>
+        <v>124556759</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,38 +2290,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491244</v>
+        <v>491181</v>
       </c>
       <c r="R17" t="n">
-        <v>6869918</v>
+        <v>6869774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556583</v>
+        <v>124556773</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -838,29 +838,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491182</v>
+        <v>491205</v>
       </c>
       <c r="R3" t="n">
-        <v>6869761</v>
+        <v>6869833</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556653</v>
+        <v>124556793</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,47 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491188</v>
+        <v>491200</v>
       </c>
       <c r="R4" t="n">
-        <v>6869772</v>
+        <v>6869830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,12 +997,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1138,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556621</v>
+        <v>124556578</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491247</v>
+        <v>491244</v>
       </c>
       <c r="R6" t="n">
-        <v>6869890</v>
+        <v>6869918</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556578</v>
+        <v>124556254</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491244</v>
+        <v>491211</v>
       </c>
       <c r="R7" t="n">
-        <v>6869918</v>
+        <v>6869621</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556618</v>
+        <v>124556621</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,50 +1336,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491195</v>
+        <v>491247</v>
       </c>
       <c r="R8" t="n">
-        <v>6869743</v>
+        <v>6869890</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1414,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556648</v>
+        <v>124556618</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,41 +1438,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491217</v>
+        <v>491195</v>
       </c>
       <c r="R9" t="n">
-        <v>6869897</v>
+        <v>6869743</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,19 +1525,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556543</v>
+        <v>124556648</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1595,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491251</v>
+        <v>491217</v>
       </c>
       <c r="R10" t="n">
-        <v>6869929</v>
+        <v>6869897</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1657,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556793</v>
+        <v>124556583</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,41 +1651,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491200</v>
+        <v>491182</v>
       </c>
       <c r="R11" t="n">
-        <v>6869830</v>
+        <v>6869761</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556551</v>
+        <v>124556457</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,47 +1762,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491196</v>
+        <v>491199</v>
       </c>
       <c r="R12" t="n">
-        <v>6869757</v>
+        <v>6869700</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556285</v>
+        <v>124556653</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,38 +1864,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491175</v>
+        <v>491188</v>
       </c>
       <c r="R13" t="n">
-        <v>6869662</v>
+        <v>6869772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556773</v>
+        <v>124556543</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1975,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,13 +2003,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491205</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6869833</v>
+        <v>6869929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556457</v>
+        <v>124556551</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,38 +2077,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491199</v>
+        <v>491196</v>
       </c>
       <c r="R15" t="n">
-        <v>6869700</v>
+        <v>6869757</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556254</v>
+        <v>124556759</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,41 +2188,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491211</v>
+        <v>491181</v>
       </c>
       <c r="R16" t="n">
-        <v>6869621</v>
+        <v>6869774</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,22 +2275,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556759</v>
+        <v>124556285</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,47 +2299,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491181</v>
+        <v>491175</v>
       </c>
       <c r="R17" t="n">
-        <v>6869774</v>
+        <v>6869662</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556793</v>
+        <v>124556285</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,34 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491200</v>
+        <v>491175</v>
       </c>
       <c r="R4" t="n">
-        <v>6869830</v>
+        <v>6869662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556441</v>
+        <v>124556254</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,50 +1021,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491201</v>
+        <v>491211</v>
       </c>
       <c r="R5" t="n">
-        <v>6869719</v>
+        <v>6869621</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556578</v>
+        <v>124556653</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,38 +1123,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491244</v>
+        <v>491188</v>
       </c>
       <c r="R6" t="n">
-        <v>6869918</v>
+        <v>6869772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,22 +1210,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556254</v>
+        <v>124556648</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491211</v>
+        <v>491217</v>
       </c>
       <c r="R7" t="n">
-        <v>6869621</v>
+        <v>6869897</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556621</v>
+        <v>124556578</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,21 +1340,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491247</v>
+        <v>491244</v>
       </c>
       <c r="R8" t="n">
-        <v>6869890</v>
+        <v>6869918</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556618</v>
+        <v>124556457</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,47 +1438,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491195</v>
+        <v>491199</v>
       </c>
       <c r="R9" t="n">
-        <v>6869743</v>
+        <v>6869700</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1537,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556648</v>
+        <v>124556618</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,41 +1540,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491217</v>
+        <v>491195</v>
       </c>
       <c r="R10" t="n">
-        <v>6869897</v>
+        <v>6869743</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,22 +1627,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556583</v>
+        <v>124556621</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,50 +1651,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491182</v>
+        <v>491247</v>
       </c>
       <c r="R11" t="n">
-        <v>6869761</v>
+        <v>6869890</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556457</v>
+        <v>124556441</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,41 +1753,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491199</v>
+        <v>491201</v>
       </c>
       <c r="R12" t="n">
-        <v>6869700</v>
+        <v>6869719</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556653</v>
+        <v>124556583</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491188</v>
+        <v>491182</v>
       </c>
       <c r="R13" t="n">
-        <v>6869772</v>
+        <v>6869761</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556543</v>
+        <v>124556793</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491200</v>
       </c>
       <c r="R14" t="n">
-        <v>6869929</v>
+        <v>6869830</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556285</v>
+        <v>124556543</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491175</v>
+        <v>491251</v>
       </c>
       <c r="R17" t="n">
-        <v>6869662</v>
+        <v>6869929</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31583-2024 artfynd.xlsx
+++ b/artfynd/A 31583-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556773</v>
+        <v>124556621</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491205</v>
+        <v>491247</v>
       </c>
       <c r="R3" t="n">
-        <v>6869833</v>
+        <v>6869890</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124556285</v>
+        <v>124556543</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,37 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491175</v>
+        <v>491251</v>
       </c>
       <c r="R4" t="n">
-        <v>6869662</v>
+        <v>6869929</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556254</v>
+        <v>124556441</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,41 +1021,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491211</v>
+        <v>491201</v>
       </c>
       <c r="R5" t="n">
-        <v>6869621</v>
+        <v>6869719</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1108,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556653</v>
+        <v>124556551</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,7 +1155,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1160,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491188</v>
+        <v>491196</v>
       </c>
       <c r="R6" t="n">
-        <v>6869772</v>
+        <v>6869757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124556648</v>
+        <v>124556457</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1258,17 +1267,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491217</v>
+        <v>491199</v>
       </c>
       <c r="R7" t="n">
-        <v>6869897</v>
+        <v>6869700</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,22 +1321,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556578</v>
+        <v>124556759</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,38 +1345,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491244</v>
+        <v>491181</v>
       </c>
       <c r="R8" t="n">
-        <v>6869918</v>
+        <v>6869774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556457</v>
+        <v>124556618</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,38 +1456,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491199</v>
+        <v>491195</v>
       </c>
       <c r="R9" t="n">
-        <v>6869700</v>
+        <v>6869743</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1528,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124556618</v>
+        <v>124556285</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,50 +1567,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491195</v>
+        <v>491175</v>
       </c>
       <c r="R10" t="n">
-        <v>6869743</v>
+        <v>6869662</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556621</v>
+        <v>124556254</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491247</v>
+        <v>491211</v>
       </c>
       <c r="R11" t="n">
-        <v>6869890</v>
+        <v>6869621</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1741,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556441</v>
+        <v>124556578</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,47 +1771,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491201</v>
+        <v>491244</v>
       </c>
       <c r="R12" t="n">
-        <v>6869719</v>
+        <v>6869918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,19 +1849,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556583</v>
+        <v>124556773</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1885,29 +1894,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491182</v>
+        <v>491205</v>
       </c>
       <c r="R13" t="n">
-        <v>6869761</v>
+        <v>6869833</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,22 +1951,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556793</v>
+        <v>124556583</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,41 +1975,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491200</v>
+        <v>491182</v>
       </c>
       <c r="R14" t="n">
-        <v>6869830</v>
+        <v>6869761</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,19 +2062,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124556551</v>
+        <v>124556653</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2100,7 +2109,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2114,13 +2123,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491196</v>
+        <v>491188</v>
       </c>
       <c r="R15" t="n">
-        <v>6869757</v>
+        <v>6869772</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556759</v>
+        <v>124556793</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,47 +2197,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumtjärnbäcken, Gumtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491181</v>
+        <v>491200</v>
       </c>
       <c r="R16" t="n">
-        <v>6869774</v>
+        <v>6869830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,19 +2275,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556543</v>
+        <v>124556648</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491251</v>
+        <v>491217</v>
       </c>
       <c r="R17" t="n">
-        <v>6869929</v>
+        <v>6869897</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
